--- a/output/graficos_nacionales/plot_nacional_regiones_e_basbrut_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_regiones_e_basbrut_a_2019.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:28</t>
+    <t xml:space="preserve">2026-09-09 21:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_regiones_e_basbrut_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_regiones_e_basbrut_a_2019.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 21:20</t>
+    <t xml:space="preserve">2026-09-18 12:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_regiones_e_basbrut_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_regiones_e_basbrut_a_2019.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 12:12</t>
+    <t xml:space="preserve">2026-10-05 19:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
